--- a/aircraft/reports/top-routes-unidirectional.xlsx
+++ b/aircraft/reports/top-routes-unidirectional.xlsx
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZRH-EWR</t>
+          <t>NCL-PMI</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NCL-PMI</t>
+          <t>ZRH-EWR</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MUC-YYZ</t>
+          <t>BCN-MAN</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BCN-MAN</t>
+          <t>MUC-YYZ</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CDG-JFK</t>
+          <t>BRU-MIA</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BRU-MIA</t>
+          <t>CDG-JFK</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EDI-GVA</t>
+          <t>GYE-AMS</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GYE-AMS</t>
+          <t>EDI-GVA</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CDG-LAX</t>
+          <t>MUC-ORD</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MUC-ORD</t>
+          <t>CDG-LAX</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GRU-AMS</t>
+          <t>PMI-MAN</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PMI-MAN</t>
+          <t>GRU-AMS</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BRS-AMS</t>
+          <t>LGG-MEM</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LGG-MEM</t>
+          <t>BRS-AMS</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MUC-CLT</t>
+          <t>IST-DUB</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EDI-PMI</t>
+          <t>MUC-EWR</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IST-DUB</t>
+          <t>MUC-CLT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FRA-IAH</t>
+          <t>MUC-IAD</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MUC-IAD</t>
+          <t>MAN-MLA</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MAN-MLA</t>
+          <t>FRA-IAH</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MUC-EWR</t>
+          <t>EDI-PMI</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EWR-FRA</t>
+          <t>MUC-JFK</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MUC-JFK</t>
+          <t>EWR-FRA</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1551,11 +1551,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ORK-AMS</t>
+          <t>JFK-LHR</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88">
@@ -1564,11 +1564,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CDG-YUL</t>
+          <t>ORK-AMS</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FRA-CUN</t>
+          <t>CDG-YUL</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EWR-MUC</t>
+          <t>FRA-CUN</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FRA-DFW</t>
+          <t>EWR-MUC</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ATH-LCA</t>
+          <t>FRA-DFW</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ORD-MUC</t>
+          <t>ATH-LCA</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LBA-ALC</t>
+          <t>ORD-MUC</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MUC-YUL</t>
+          <t>LBA-ALC</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FRA-MIA</t>
+          <t>MUC-YUL</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IST-JFK</t>
+          <t>FRA-MIA</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JFK-LHR</t>
+          <t>IST-JFK</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MAN-REU</t>
+          <t>NCL-IBZ</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ISL-SNN</t>
+          <t>MAN-REU</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LGW-RMU</t>
+          <t>ISL-SNN</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>AMS-UIO</t>
+          <t>LGW-RMU</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>BHX-AGP</t>
+          <t>AMS-UIO</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MAN-LHR</t>
+          <t>BHX-AGP</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ZRH-YYZ</t>
+          <t>MAN-LHR</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SFO-FRA</t>
+          <t>ZRH-YYZ</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3007,11 +3007,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>NCL-IBZ</t>
+          <t>SFO-FRA</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DFW-LUX</t>
+          <t>PIK-PMI</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>BRU-CVG</t>
+          <t>DFW-LUX</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DFW-FRA</t>
+          <t>BRU-CVG</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>LHR-IST</t>
+          <t>DFW-FRA</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PIK-PMI</t>
+          <t>BHX-GVA</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>GCI-EMA</t>
+          <t>LHR-IST</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BHX-GVA</t>
+          <t>GCI-EMA</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>LHR-YYZ</t>
+          <t>EMA-GCI</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EMA-GCI</t>
+          <t>LHR-YYZ</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>AMS-YYZ</t>
+          <t>MUC-ATL</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>LIS-LHR</t>
+          <t>AMS-YYZ</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>LHR-LCA</t>
+          <t>LIS-LHR</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MUC-ATL</t>
+          <t>LHR-LCA</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PMI-LBA</t>
+          <t>YYZ-MUC</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YYZ-MUC</t>
+          <t>PMI-LBA</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>LHR-ATH</t>
+          <t>FRA-LCA</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>LHR-BRU</t>
+          <t>AGP-LGW</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>YYZ-LGW</t>
+          <t>YYC-CDG</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>JFK-DXB</t>
+          <t>YYZ-LGW</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>YYC-CDG</t>
+          <t>DXB-JFK</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>DXB-JFK</t>
+          <t>JFK-DXB</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>ZAG-DUB</t>
+          <t>LHR-ZRH</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>BRU-CUN</t>
+          <t>ZAG-DUB</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>LHR-ZRH</t>
+          <t>LHR-BRU</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>LPL-IBZ</t>
+          <t>VIE-LCA</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>FRA-LCA</t>
+          <t>BRU-CUN</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>SKG-LCA</t>
+          <t>LPL-IBZ</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>VIE-LCA</t>
+          <t>ALC-LGW</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>ALC-LGW</t>
+          <t>LIN-LHR</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>LIN-LHR</t>
+          <t>IST-YUL</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>IST-YUL</t>
+          <t>LHR-ARN</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>ATH-DUB</t>
+          <t>GVA-LGW</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>GVA-LGW</t>
+          <t>SKG-LCA</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>AGP-LGW</t>
+          <t>EWR-LHR</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>LHR-ARN</t>
+          <t>IAH-LHR</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>EWR-LHR</t>
+          <t>DUB-CIA</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>CRL-ORK</t>
+          <t>BQN-AMS</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>OSL-LHR</t>
+          <t>GLA-SOU</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>DUB-CIA</t>
+          <t>LHR-ATH</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>BQN-AMS</t>
+          <t>VCE-LGW</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>YYC-LGW</t>
+          <t>LBA-CDG</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>BOS-FRA</t>
+          <t>BGY-DUB</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>IAH-LHR</t>
+          <t>CPH-LGW</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>AMM-JFK</t>
+          <t>BOS-FRA</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>LBA-CDG</t>
+          <t>YYC-LGW</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>BGY-DUB</t>
+          <t>AMM-JFK</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>CPH-LGW</t>
+          <t>OSL-LHR</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>GLA-SOU</t>
+          <t>CRL-ORK</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>VCE-LGW</t>
+          <t>ATH-DUB</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EMA-LPA</t>
+          <t>BHX-FCO</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>MAD-MAN</t>
+          <t>PVG-LHR</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>PVG-LHR</t>
+          <t>MAD-MAN</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>BHX-FCO</t>
+          <t>EMA-LPA</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>BOM-LHR</t>
+          <t>YYZ-IST</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>LCK-LUX</t>
+          <t>JER-LGW</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>EDI-ORY</t>
+          <t>VIE-YUL</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PHL-CGN</t>
+          <t>EDI-ORY</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>VIE-YUL</t>
+          <t>PHL-CGN</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>LHR-HAM</t>
+          <t>MAN-VLC</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>MRS-DUB</t>
+          <t>LHR-HAM</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>MAN-VLC</t>
+          <t>MRS-DUB</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>AMS-MEX</t>
+          <t>BOM-LHR</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>YYZ-IST</t>
+          <t>AMS-MEX</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>JER-LGW</t>
+          <t>PTY-LGG</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>BHX-FUE</t>
+          <t>LHR-SFO</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>CPH-LCA</t>
+          <t>MAN-BSL</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>ZRH-YUL</t>
+          <t>CDG-MAN</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>HSV-LUX</t>
+          <t>BOS-MUC</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>IAD-IST</t>
+          <t>BHX-MAH</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>JFK-AMS</t>
+          <t>EDI-CRL</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>JER-MAN</t>
+          <t>LHR-CPH</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>LHR-CPH</t>
+          <t>LHR-ABZ</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>EDI-CRL</t>
+          <t>GCI-MAN</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>MAN-BSL</t>
+          <t>BHX-FNC</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>BHX-FNC</t>
+          <t>HSV-LUX</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>LHR-FCO</t>
+          <t>ZRH-YUL</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>BHX-MAH</t>
+          <t>IAD-IST</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>BOS-MUC</t>
+          <t>JFK-AMS</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>PTY-LGG</t>
+          <t>JER-MAN</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>LHR-SFO</t>
+          <t>BHX-FUE</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>FCO-LHR</t>
+          <t>LHR-FCO</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>IST-ATL</t>
+          <t>CPH-LCA</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>CDG-MAN</t>
+          <t>FCO-LHR</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>BRU-LHR</t>
+          <t>IST-ATL</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>LHR-DUS</t>
+          <t>BRU-LHR</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>LHR-HEL</t>
+          <t>LCK-LUX</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>GCI-MAN</t>
+          <t>LHR-DUS</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -6517,11 +6517,11 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>MAN-JED</t>
+          <t>LHR-HEL</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="470">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>GSP-FRA</t>
+          <t>BHX-LCA</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>ZRH-SFO</t>
+          <t>PUJ-FRA</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>BUD-LGW</t>
+          <t>NAP-DUB</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>MAD-LGW</t>
+          <t>MAN-HER</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>ZRH-PHL</t>
+          <t>GSP-FRA</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>MAN-HER</t>
+          <t>CEG-TLS</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>LAS-LGW</t>
+          <t>JFK-CDG</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>DFW-DOH</t>
+          <t>BCN-LHR</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>LGG-IND</t>
+          <t>ZRH-SFO</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>GCI-BHX</t>
+          <t>MAN-JED</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>MAN-CTA</t>
+          <t>BUD-LGW</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>CEG-TLS</t>
+          <t>MAD-LGW</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>JFK-CDG</t>
+          <t>LGG-IND</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>BCN-LHR</t>
+          <t>IAD-LHR</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>NAP-DUB</t>
+          <t>ZRH-PHL</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>BRS-POZ</t>
+          <t>MST-ATL</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>MST-ATL</t>
+          <t>BRS-POZ</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>IAD-LHR</t>
+          <t>JER-EMA</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>JER-EMA</t>
+          <t>GCI-BHX</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>BHX-LCA</t>
+          <t>DFW-DOH</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>PUJ-FRA</t>
+          <t>LAS-LGW</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>BEG-LCA</t>
+          <t>MAN-CTA</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>DUB-VCE</t>
+          <t>BEG-LCA</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MAN-LEI</t>
+          <t>DUB-VCE</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>YUL-FRA</t>
+          <t>MAN-LEI</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>WRT-FAB</t>
+          <t>DEL-LHR</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>LHR-VCE</t>
+          <t>WRT-FAB</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>BER-LHR</t>
+          <t>LHR-VCE</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>DXB-BOS</t>
+          <t>BER-LHR</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>ORD-ZRH</t>
+          <t>DXB-BOS</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>ZRH-BOS</t>
+          <t>ORD-ZRH</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>EMA-JER</t>
+          <t>ZRH-BOS</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>GLA-LHR</t>
+          <t>EMA-JER</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>BHD-LHR</t>
+          <t>GLA-LHR</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>TPA-FRA</t>
+          <t>BHD-LHR</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>DUB-LIN</t>
+          <t>TPA-FRA</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>IST-IAH</t>
+          <t>DUB-LIN</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>DEL-LHR</t>
+          <t>YUL-FRA</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>ABZ-ALC</t>
+          <t>IST-IAH</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>MAN-GCI</t>
+          <t>ABZ-ALC</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>MAN-AYT</t>
+          <t>MAN-GCI</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>ABZ-LHR</t>
+          <t>MAN-AYT</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>DOH-LHR</t>
+          <t>ABZ-LHR</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>LHR-ABZ</t>
+          <t>DOH-LHR</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>BHX-GCI</t>
+          <t>CDG-LGW</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>LIN-DUB</t>
+          <t>FRA-ORK</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>NCL-MAH</t>
+          <t>POZ-ORK</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>IBZ-EDI</t>
+          <t>GLA-BCN</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>BHX-RHO</t>
+          <t>SJO-FRA</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>CDG-LGW</t>
+          <t>EWR-DEL</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>CRL-DUB</t>
+          <t>MIA-LGG</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>EWR-DEL</t>
+          <t>BHX-GCI</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>SJO-FRA</t>
+          <t>LIN-DUB</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>GLA-BCN</t>
+          <t>NCL-MAH</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>POZ-ORK</t>
+          <t>IBZ-EDI</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>JFK-MXP</t>
+          <t>BHX-RHO</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>REU-GLA</t>
+          <t>LGW-AMS</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>BRS-WRO</t>
+          <t>CDG-MSP</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>SFO-ZRH</t>
+          <t>BUD-SNN</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>BUD-SNN</t>
+          <t>CRL-DUB</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>FRA-ORK</t>
+          <t>JFK-MXP</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>CDG-MSP</t>
+          <t>REU-GLA</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>LGW-AMS</t>
+          <t>SFO-ZRH</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MIA-LGG</t>
+          <t>BRS-WRO</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>LUX-ORD</t>
+          <t>CDG-YVR</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>KRK-SNN</t>
+          <t>LUX-ORD</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>BRS-WMI</t>
+          <t>RUH-IAD</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>DTW-CDG</t>
+          <t>BRS-WMI</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>CDG-YVR</t>
+          <t>DUB-BLQ</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>LUX-ATL</t>
+          <t>STN-KIR</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>STN-KIR</t>
+          <t>DTW-CDG</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>DUB-BLQ</t>
+          <t>KRK-SNN</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>RUH-IAD</t>
+          <t>LUX-ATL</t>
         </is>
       </c>
       <c r="C550" t="n">

--- a/aircraft/reports/top-routes-unidirectional.xlsx
+++ b/aircraft/reports/top-routes-unidirectional.xlsx
@@ -9793,7 +9793,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>AGP-EDI</t>
+          <t>ORD-HHN</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>IAH-DXB</t>
+          <t>AGP-EDI</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>DUB-TRN</t>
+          <t>IAH-DXB</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>LGW-PMI</t>
+          <t>DUB-TRN</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>HUY-PMI</t>
+          <t>LGW-PMI</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>ATH-JFK</t>
+          <t>KEF-LGG</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>PSA-DUB</t>
+          <t>ATH-JFK</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>TLV-LHR</t>
+          <t>PSA-DUB</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>ORD-HHN</t>
+          <t>TLV-LHR</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>WAW-PUJ</t>
+          <t>HUY-PMI</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>MUC-LAX</t>
+          <t>WAW-PUJ</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>ORD-AMM</t>
+          <t>BRS-ALC</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>MAN-DXB</t>
+          <t>ORD-AMM</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>BRS-ALC</t>
+          <t>MAN-DXB</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>LCA-BEG</t>
+          <t>ARN-LPA</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>ARN-LPA</t>
+          <t>LCA-BEG</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>LCA-WAW</t>
+          <t>PHL-LHR</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>LCA-CPH</t>
+          <t>LCA-WAW</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>PHL-LHR</t>
+          <t>LCA-CPH</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>DUB-PRG</t>
+          <t>HHN-RFD</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>AGP-BHX</t>
+          <t>ATL-DOH</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>FRA-NLU</t>
+          <t>YUL-DOH</t>
         </is>
       </c>
       <c r="C837" t="n">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>YUL-DOH</t>
+          <t>FRA-NLU</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>ATH-YUL</t>
+          <t>TFS-LGW</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>ATL-MUC</t>
+          <t>ATH-YUL</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>DXB-EWR</t>
+          <t>ATL-MUC</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>LBA-GRO</t>
+          <t>DXB-EWR</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>LHR-SEA</t>
+          <t>LBA-GRO</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>MAN-VRN</t>
+          <t>LHR-SEA</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>MAN-LYS</t>
+          <t>MAN-VRN</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>OST-JFK</t>
+          <t>MAN-LYS</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>TFS-LGW</t>
+          <t>OST-JFK</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>JED-YYZ</t>
+          <t>LHR-HKG</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>MAN-GNB</t>
+          <t>JED-YYZ</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>BRS-BZG</t>
+          <t>MAN-GNB</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>ATL-ISL</t>
+          <t>BRS-BZG</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>LHR-HKG</t>
+          <t>ATL-ISL</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>MAN-DUB</t>
+          <t>NTE-EDI</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>MAN-SOU</t>
+          <t>MAN-DUB</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>DUB-MRS</t>
+          <t>MAN-SOU</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>NTE-EDI</t>
+          <t>DUB-MRS</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>HHN-RFD</t>
+          <t>AGP-BHX</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>FRA-RDU</t>
+          <t>LIG-MAN</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>STR-LHR</t>
+          <t>CDG-LCA</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>IAH-IST</t>
+          <t>JTR-LHR</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>ORK-GDN</t>
+          <t>LTN-CDG</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>LPL-LGW</t>
+          <t>NTE-MAN</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>CDG-LCA</t>
+          <t>MXP-LHR</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>JTR-LHR</t>
+          <t>VIE-BOS</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>KIR-HHN</t>
+          <t>PHL-DOH</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>NTE-MAN</t>
+          <t>YYC-FRA</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>MXP-LHR</t>
+          <t>PMI-BHX</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>LTN-CDG</t>
+          <t>GLA-FCO</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>LCY-AMS</t>
+          <t>ORK-GDN</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>VIE-BOS</t>
+          <t>WAW-MIA</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>PHL-DOH</t>
+          <t>LCY-AMS</t>
         </is>
       </c>
       <c r="C877" t="n">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>YYC-FRA</t>
+          <t>FRA-RDU</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>PMI-BHX</t>
+          <t>BRU-BGR</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>LIG-MAN</t>
+          <t>KIR-HHN</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>GLA-FCO</t>
+          <t>SFO-ORY</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>BRU-BGR</t>
+          <t>AMS-BGI</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>SFO-ORY</t>
+          <t>DUB-CCF</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>LHR-BWI</t>
+          <t>MUC-LAX</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>BHX-OPO</t>
+          <t>LPL-LGW</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>ATL-DOH</t>
+          <t>DUB-PRG</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>DUS-LCA</t>
+          <t>LEJ-CVG</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>LTN-KIR</t>
+          <t>EMA-CIA</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>BOS-DXB</t>
+          <t>SEA-FRA</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>EMA-CIA</t>
+          <t>BGO-LPA</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>NAP-EWR</t>
+          <t>BOS-DXB</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>BGO-LPA</t>
+          <t>STR-LHR</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>SEA-FRA</t>
+          <t>LTN-KIR</t>
         </is>
       </c>
       <c r="C893" t="n">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>LEJ-CVG</t>
+          <t>SOU-MAN</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>SOU-MAN</t>
+          <t>TRN-DUB</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>TRN-DUB</t>
+          <t>DUS-LCA</t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>DUB-CCF</t>
+          <t>EMA-FUE</t>
         </is>
       </c>
       <c r="C897" t="n">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>EMA-FUE</t>
+          <t>NAP-EWR</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>AMS-BGI</t>
+          <t>BHX-OPO</t>
         </is>
       </c>
       <c r="C899" t="n">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>WAW-MIA</t>
+          <t>LHR-BWI</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -12133,11 +12133,11 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>FAO-LGW</t>
+          <t>IAH-IST</t>
         </is>
       </c>
       <c r="C901" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="902">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>LCY-BHD</t>
+          <t>BRS-GDN</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>LGW-LIN</t>
+          <t>CUN-LGW</t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>CUN-LGW</t>
+          <t>LCY-BHD</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>LGW-MLA</t>
+          <t>LGW-LIN</t>
         </is>
       </c>
       <c r="C905" t="n">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>AMS-PUJ</t>
+          <t>FAO-LGW</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>LHR-TLV</t>
+          <t>LGW-MLA</t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>PUJ-WAW</t>
+          <t>LPL-BVA</t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>ATL-IST</t>
+          <t>CGN-CVG</t>
         </is>
       </c>
       <c r="C909" t="n">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>LHR-ADD</t>
+          <t>LGW-ARN</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>EWR-ZRH</t>
+          <t>NCL-FAB</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>NCL-FAB</t>
+          <t>AMS-PUJ</t>
         </is>
       </c>
       <c r="C912" t="n">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>CGN-CVG</t>
+          <t>LHR-TLV</t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>LGW-ARN</t>
+          <t>ATL-IST</t>
         </is>
       </c>
       <c r="C914" t="n">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>LPL-BVA</t>
+          <t>LHR-ADD</t>
         </is>
       </c>
       <c r="C915" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>BRS-GDN</t>
+          <t>EWR-ZRH</t>
         </is>
       </c>
       <c r="C916" t="n">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>LGW-BGI</t>
+          <t>PUJ-WAW</t>
         </is>
       </c>
       <c r="C917" t="n">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>INV-MAN</t>
+          <t>LGW-BGI</t>
         </is>
       </c>
       <c r="C918" t="n">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>MAN-INN</t>
+          <t>INV-MAN</t>
         </is>
       </c>
       <c r="C919" t="n">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>PSA-MAN</t>
+          <t>DXB-YYZ</t>
         </is>
       </c>
       <c r="C920" t="n">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>CDG-KEF</t>
+          <t>STN-SDF</t>
         </is>
       </c>
       <c r="C921" t="n">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>LGW-FUE</t>
+          <t>PSA-MAN</t>
         </is>
       </c>
       <c r="C922" t="n">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>LGG-RFD</t>
+          <t>CDG-KEF</t>
         </is>
       </c>
       <c r="C923" t="n">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>LHR-ZAG</t>
+          <t>LGW-FUE</t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>FRA-MBJ</t>
+          <t>LGG-RFD</t>
         </is>
       </c>
       <c r="C925" t="n">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>MUC-ORK</t>
+          <t>LHR-ZAG</t>
         </is>
       </c>
       <c r="C926" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>MAN-TSF</t>
+          <t>FRA-MBJ</t>
         </is>
       </c>
       <c r="C927" t="n">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>EMA-BGY</t>
+          <t>MUC-ORK</t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>DUB-DXB</t>
+          <t>MAN-TSF</t>
         </is>
       </c>
       <c r="C929" t="n">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>DUS-LRM</t>
+          <t>EMA-BGY</t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>KEF-LGG</t>
+          <t>DUB-DXB</t>
         </is>
       </c>
       <c r="C931" t="n">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>MAN-CPH</t>
+          <t>DUS-LRM</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>DUB-TSF</t>
+          <t>MAN-CPH</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>MIA-MUC</t>
+          <t>DUB-TSF</t>
         </is>
       </c>
       <c r="C934" t="n">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>BGY-NOC</t>
+          <t>MIA-MUC</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>KTW-CUN</t>
+          <t>BGY-NOC</t>
         </is>
       </c>
       <c r="C936" t="n">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>STN-SDF</t>
+          <t>KTW-CUN</t>
         </is>
       </c>
       <c r="C937" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>STR-LGW</t>
+          <t>MAN-INN</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>DXB-YYZ</t>
+          <t>STR-LGW</t>
         </is>
       </c>
       <c r="C939" t="n">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>AMS-DUB</t>
+          <t>BUD-MAN</t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>DXB-MAN</t>
+          <t>AMS-DUB</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>MLA-LHR</t>
+          <t>DXB-MAN</t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>MAN-DOH</t>
+          <t>MLA-LHR</t>
         </is>
       </c>
       <c r="C944" t="n">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>ZRH-LGW</t>
+          <t>MAN-DOH</t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>MUC-MAN</t>
+          <t>ZRH-LGW</t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>MAN-BHD</t>
+          <t>MUC-MAN</t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>BUD-MAN</t>
+          <t>MAN-BHD</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>LHR-INV</t>
+          <t>LHR-LAS</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>OTP-LHR</t>
+          <t>LHR-INV</t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>VIE-CUN</t>
+          <t>OTP-LHR</t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>DUB-IST</t>
+          <t>VIE-CUN</t>
         </is>
       </c>
       <c r="C953" t="n">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>DXB-IAH</t>
+          <t>DUB-IST</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>CUN-VIE</t>
+          <t>DXB-IAH</t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>OPO-LHR</t>
+          <t>CUN-VIE</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>LHR-LAS</t>
+          <t>OPO-LHR</t>
         </is>
       </c>
       <c r="C957" t="n">

--- a/aircraft/reports/top-routes-unidirectional.xlsx
+++ b/aircraft/reports/top-routes-unidirectional.xlsx
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NCL-PMI</t>
+          <t>ZRH-EWR</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZRH-EWR</t>
+          <t>NCL-PMI</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BCN-MAN</t>
+          <t>MUC-YYZ</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MUC-YYZ</t>
+          <t>BCN-MAN</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BRU-MIA</t>
+          <t>CDG-JFK</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CDG-JFK</t>
+          <t>BRU-MIA</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GYE-AMS</t>
+          <t>EDI-GVA</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EDI-GVA</t>
+          <t>GYE-AMS</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MUC-ORD</t>
+          <t>CDG-LAX</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CDG-LAX</t>
+          <t>MUC-ORD</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PMI-MAN</t>
+          <t>GRU-AMS</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GRU-AMS</t>
+          <t>PMI-MAN</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LGG-MEM</t>
+          <t>BRS-AMS</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BRS-AMS</t>
+          <t>LGG-MEM</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IST-DUB</t>
+          <t>MUC-CLT</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MUC-EWR</t>
+          <t>EDI-PMI</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MUC-CLT</t>
+          <t>IST-DUB</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MUC-IAD</t>
+          <t>FRA-IAH</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MAN-MLA</t>
+          <t>MUC-IAD</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FRA-IAH</t>
+          <t>MAN-MLA</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EDI-PMI</t>
+          <t>MUC-EWR</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MUC-JFK</t>
+          <t>EWR-FRA</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EWR-FRA</t>
+          <t>MUC-JFK</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1551,11 +1551,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JFK-LHR</t>
+          <t>ORK-AMS</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88">
@@ -1564,11 +1564,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ORK-AMS</t>
+          <t>CDG-YUL</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CDG-YUL</t>
+          <t>FRA-CUN</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FRA-CUN</t>
+          <t>EWR-MUC</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EWR-MUC</t>
+          <t>FRA-DFW</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FRA-DFW</t>
+          <t>ATH-LCA</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ATH-LCA</t>
+          <t>ORD-MUC</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ORD-MUC</t>
+          <t>LBA-ALC</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LBA-ALC</t>
+          <t>MUC-YUL</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MUC-YUL</t>
+          <t>FRA-MIA</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FRA-MIA</t>
+          <t>IST-JFK</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IST-JFK</t>
+          <t>JFK-LHR</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NCL-IBZ</t>
+          <t>MAN-REU</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MAN-REU</t>
+          <t>ISL-SNN</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ISL-SNN</t>
+          <t>LGW-RMU</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LGW-RMU</t>
+          <t>AMS-UIO</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>AMS-UIO</t>
+          <t>BHX-AGP</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BHX-AGP</t>
+          <t>MAN-LHR</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MAN-LHR</t>
+          <t>ZRH-YYZ</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ZRH-YYZ</t>
+          <t>SFO-FRA</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3007,11 +3007,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SFO-FRA</t>
+          <t>NCL-IBZ</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="200">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PIK-PMI</t>
+          <t>DFW-LUX</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DFW-LUX</t>
+          <t>BRU-CVG</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BRU-CVG</t>
+          <t>DFW-FRA</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DFW-FRA</t>
+          <t>LHR-IST</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>BHX-GVA</t>
+          <t>PIK-PMI</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>LHR-IST</t>
+          <t>GCI-EMA</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>GCI-EMA</t>
+          <t>BHX-GVA</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>EMA-GCI</t>
+          <t>LHR-YYZ</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>LHR-YYZ</t>
+          <t>EMA-GCI</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MUC-ATL</t>
+          <t>AMS-YYZ</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>AMS-YYZ</t>
+          <t>LIS-LHR</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>LIS-LHR</t>
+          <t>LHR-LCA</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>LHR-LCA</t>
+          <t>MUC-ATL</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YYZ-MUC</t>
+          <t>PMI-LBA</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PMI-LBA</t>
+          <t>YYZ-MUC</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>FRA-LCA</t>
+          <t>LHR-ATH</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>AGP-LGW</t>
+          <t>LHR-BRU</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>YYC-CDG</t>
+          <t>YYZ-LGW</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>YYZ-LGW</t>
+          <t>JFK-DXB</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>DXB-JFK</t>
+          <t>YYC-CDG</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>JFK-DXB</t>
+          <t>DXB-JFK</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>LHR-ZRH</t>
+          <t>ZAG-DUB</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>ZAG-DUB</t>
+          <t>BRU-CUN</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>LHR-BRU</t>
+          <t>LHR-ZRH</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>VIE-LCA</t>
+          <t>LPL-IBZ</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>BRU-CUN</t>
+          <t>FRA-LCA</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>LPL-IBZ</t>
+          <t>SKG-LCA</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>ALC-LGW</t>
+          <t>VIE-LCA</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>LIN-LHR</t>
+          <t>ALC-LGW</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>IST-YUL</t>
+          <t>LIN-LHR</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>LHR-ARN</t>
+          <t>IST-YUL</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>GVA-LGW</t>
+          <t>ATH-DUB</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>SKG-LCA</t>
+          <t>GVA-LGW</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>EWR-LHR</t>
+          <t>AGP-LGW</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>IAH-LHR</t>
+          <t>LHR-ARN</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>DUB-CIA</t>
+          <t>EWR-LHR</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>BQN-AMS</t>
+          <t>CRL-ORK</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>GLA-SOU</t>
+          <t>OSL-LHR</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>LHR-ATH</t>
+          <t>DUB-CIA</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>VCE-LGW</t>
+          <t>BQN-AMS</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>LBA-CDG</t>
+          <t>YYC-LGW</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>BGY-DUB</t>
+          <t>BOS-FRA</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CPH-LGW</t>
+          <t>IAH-LHR</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>BOS-FRA</t>
+          <t>AMM-JFK</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>YYC-LGW</t>
+          <t>LBA-CDG</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>AMM-JFK</t>
+          <t>BGY-DUB</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>OSL-LHR</t>
+          <t>CPH-LGW</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>CRL-ORK</t>
+          <t>GLA-SOU</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>ATH-DUB</t>
+          <t>VCE-LGW</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>BHX-FCO</t>
+          <t>EMA-LPA</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>PVG-LHR</t>
+          <t>MAD-MAN</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>MAD-MAN</t>
+          <t>PVG-LHR</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>EMA-LPA</t>
+          <t>BHX-FCO</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>YYZ-IST</t>
+          <t>BOM-LHR</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>JER-LGW</t>
+          <t>LCK-LUX</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>VIE-YUL</t>
+          <t>EDI-ORY</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>EDI-ORY</t>
+          <t>PHL-CGN</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PHL-CGN</t>
+          <t>VIE-YUL</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>MAN-VLC</t>
+          <t>LHR-HAM</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>LHR-HAM</t>
+          <t>MRS-DUB</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>MRS-DUB</t>
+          <t>MAN-VLC</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>BOM-LHR</t>
+          <t>AMS-MEX</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>AMS-MEX</t>
+          <t>YYZ-IST</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>PTY-LGG</t>
+          <t>JER-LGW</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>LHR-SFO</t>
+          <t>BHX-FUE</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MAN-BSL</t>
+          <t>CPH-LCA</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>CDG-MAN</t>
+          <t>ZRH-YUL</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>BOS-MUC</t>
+          <t>HSV-LUX</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>BHX-MAH</t>
+          <t>IAD-IST</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>EDI-CRL</t>
+          <t>JFK-AMS</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>LHR-CPH</t>
+          <t>JER-MAN</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>LHR-ABZ</t>
+          <t>LHR-CPH</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>GCI-MAN</t>
+          <t>EDI-CRL</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>BHX-FNC</t>
+          <t>MAN-BSL</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>HSV-LUX</t>
+          <t>BHX-FNC</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>ZRH-YUL</t>
+          <t>LHR-FCO</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>IAD-IST</t>
+          <t>BHX-MAH</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>JFK-AMS</t>
+          <t>BOS-MUC</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>JER-MAN</t>
+          <t>PTY-LGG</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>BHX-FUE</t>
+          <t>LHR-SFO</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>LHR-FCO</t>
+          <t>FCO-LHR</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>CPH-LCA</t>
+          <t>IST-ATL</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>FCO-LHR</t>
+          <t>CDG-MAN</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>IST-ATL</t>
+          <t>BRU-LHR</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>BRU-LHR</t>
+          <t>LHR-DUS</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>LCK-LUX</t>
+          <t>LHR-HEL</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>LHR-DUS</t>
+          <t>GCI-MAN</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -6517,11 +6517,11 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>LHR-HEL</t>
+          <t>MAN-JED</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="470">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>BHX-LCA</t>
+          <t>GSP-FRA</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>PUJ-FRA</t>
+          <t>ZRH-SFO</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>NAP-DUB</t>
+          <t>BUD-LGW</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>MAN-HER</t>
+          <t>MAD-LGW</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>GSP-FRA</t>
+          <t>ZRH-PHL</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>CEG-TLS</t>
+          <t>MAN-HER</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>JFK-CDG</t>
+          <t>LAS-LGW</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>BCN-LHR</t>
+          <t>DFW-DOH</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>ZRH-SFO</t>
+          <t>LGG-IND</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>MAN-JED</t>
+          <t>GCI-BHX</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>BUD-LGW</t>
+          <t>MAN-CTA</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>MAD-LGW</t>
+          <t>CEG-TLS</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>LGG-IND</t>
+          <t>JFK-CDG</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>IAD-LHR</t>
+          <t>BCN-LHR</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>ZRH-PHL</t>
+          <t>NAP-DUB</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>MST-ATL</t>
+          <t>BRS-POZ</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>BRS-POZ</t>
+          <t>MST-ATL</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>JER-EMA</t>
+          <t>IAD-LHR</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>GCI-BHX</t>
+          <t>JER-EMA</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>DFW-DOH</t>
+          <t>BHX-LCA</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>LAS-LGW</t>
+          <t>PUJ-FRA</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MAN-CTA</t>
+          <t>BEG-LCA</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>BEG-LCA</t>
+          <t>DUB-VCE</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>DUB-VCE</t>
+          <t>MAN-LEI</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MAN-LEI</t>
+          <t>YUL-FRA</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>DEL-LHR</t>
+          <t>WRT-FAB</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>WRT-FAB</t>
+          <t>LHR-VCE</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>LHR-VCE</t>
+          <t>BER-LHR</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>BER-LHR</t>
+          <t>DXB-BOS</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>DXB-BOS</t>
+          <t>ORD-ZRH</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>ORD-ZRH</t>
+          <t>ZRH-BOS</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>ZRH-BOS</t>
+          <t>EMA-JER</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>EMA-JER</t>
+          <t>GLA-LHR</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>GLA-LHR</t>
+          <t>BHD-LHR</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>BHD-LHR</t>
+          <t>TPA-FRA</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>TPA-FRA</t>
+          <t>DUB-LIN</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>DUB-LIN</t>
+          <t>IST-IAH</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>YUL-FRA</t>
+          <t>DEL-LHR</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>IST-IAH</t>
+          <t>ABZ-ALC</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>ABZ-ALC</t>
+          <t>MAN-GCI</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>MAN-GCI</t>
+          <t>MAN-AYT</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>MAN-AYT</t>
+          <t>ABZ-LHR</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>ABZ-LHR</t>
+          <t>DOH-LHR</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>DOH-LHR</t>
+          <t>LHR-ABZ</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>CDG-LGW</t>
+          <t>BHX-GCI</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>FRA-ORK</t>
+          <t>LIN-DUB</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>POZ-ORK</t>
+          <t>NCL-MAH</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>GLA-BCN</t>
+          <t>IBZ-EDI</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>SJO-FRA</t>
+          <t>BHX-RHO</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>EWR-DEL</t>
+          <t>CDG-LGW</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>MIA-LGG</t>
+          <t>CRL-DUB</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>BHX-GCI</t>
+          <t>EWR-DEL</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>LIN-DUB</t>
+          <t>SJO-FRA</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>NCL-MAH</t>
+          <t>GLA-BCN</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>IBZ-EDI</t>
+          <t>POZ-ORK</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>BHX-RHO</t>
+          <t>JFK-MXP</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>LGW-AMS</t>
+          <t>REU-GLA</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>CDG-MSP</t>
+          <t>BRS-WRO</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>BUD-SNN</t>
+          <t>SFO-ZRH</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>CRL-DUB</t>
+          <t>BUD-SNN</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>JFK-MXP</t>
+          <t>FRA-ORK</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>REU-GLA</t>
+          <t>CDG-MSP</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>SFO-ZRH</t>
+          <t>LGW-AMS</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>BRS-WRO</t>
+          <t>MIA-LGG</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>CDG-YVR</t>
+          <t>LUX-ORD</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>LUX-ORD</t>
+          <t>KRK-SNN</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>RUH-IAD</t>
+          <t>BRS-WMI</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>BRS-WMI</t>
+          <t>DTW-CDG</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>DUB-BLQ</t>
+          <t>CDG-YVR</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>STN-KIR</t>
+          <t>LUX-ATL</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>DTW-CDG</t>
+          <t>STN-KIR</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>KRK-SNN</t>
+          <t>DUB-BLQ</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>LUX-ATL</t>
+          <t>RUH-IAD</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>ORD-HHN</t>
+          <t>AGP-EDI</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>AGP-EDI</t>
+          <t>IAH-DXB</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>IAH-DXB</t>
+          <t>DUB-TRN</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>DUB-TRN</t>
+          <t>LGW-PMI</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>LGW-PMI</t>
+          <t>HUY-PMI</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>KEF-LGG</t>
+          <t>ATH-JFK</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>ATH-JFK</t>
+          <t>PSA-DUB</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>PSA-DUB</t>
+          <t>TLV-LHR</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>TLV-LHR</t>
+          <t>ORD-HHN</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>HUY-PMI</t>
+          <t>WAW-PUJ</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>WAW-PUJ</t>
+          <t>MUC-LAX</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>BRS-ALC</t>
+          <t>ORD-AMM</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ORD-AMM</t>
+          <t>MAN-DXB</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>MAN-DXB</t>
+          <t>BRS-ALC</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>ARN-LPA</t>
+          <t>LCA-BEG</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>LCA-BEG</t>
+          <t>ARN-LPA</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>PHL-LHR</t>
+          <t>LCA-WAW</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>LCA-WAW</t>
+          <t>LCA-CPH</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>LCA-CPH</t>
+          <t>PHL-LHR</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>HHN-RFD</t>
+          <t>DUB-PRG</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>ATL-DOH</t>
+          <t>AGP-BHX</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>YUL-DOH</t>
+          <t>FRA-NLU</t>
         </is>
       </c>
       <c r="C837" t="n">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>FRA-NLU</t>
+          <t>YUL-DOH</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>TFS-LGW</t>
+          <t>ATH-YUL</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>ATH-YUL</t>
+          <t>ATL-MUC</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>ATL-MUC</t>
+          <t>DXB-EWR</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>DXB-EWR</t>
+          <t>LBA-GRO</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>LBA-GRO</t>
+          <t>LHR-SEA</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>LHR-SEA</t>
+          <t>MAN-VRN</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>MAN-VRN</t>
+          <t>MAN-LYS</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>MAN-LYS</t>
+          <t>OST-JFK</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>OST-JFK</t>
+          <t>TFS-LGW</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>LHR-HKG</t>
+          <t>JED-YYZ</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>JED-YYZ</t>
+          <t>MAN-GNB</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>MAN-GNB</t>
+          <t>BRS-BZG</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>BRS-BZG</t>
+          <t>ATL-ISL</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>ATL-ISL</t>
+          <t>LHR-HKG</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>NTE-EDI</t>
+          <t>MAN-DUB</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>MAN-DUB</t>
+          <t>MAN-SOU</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>MAN-SOU</t>
+          <t>DUB-MRS</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>DUB-MRS</t>
+          <t>NTE-EDI</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>AGP-BHX</t>
+          <t>HHN-RFD</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>LIG-MAN</t>
+          <t>FRA-RDU</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>CDG-LCA</t>
+          <t>STR-LHR</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>JTR-LHR</t>
+          <t>IAH-IST</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>LTN-CDG</t>
+          <t>ORK-GDN</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>NTE-MAN</t>
+          <t>LPL-LGW</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>MXP-LHR</t>
+          <t>CDG-LCA</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>VIE-BOS</t>
+          <t>JTR-LHR</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>PHL-DOH</t>
+          <t>KIR-HHN</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>YYC-FRA</t>
+          <t>NTE-MAN</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>PMI-BHX</t>
+          <t>MXP-LHR</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>GLA-FCO</t>
+          <t>LTN-CDG</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>ORK-GDN</t>
+          <t>LCY-AMS</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>WAW-MIA</t>
+          <t>VIE-BOS</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>LCY-AMS</t>
+          <t>PHL-DOH</t>
         </is>
       </c>
       <c r="C877" t="n">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>FRA-RDU</t>
+          <t>YYC-FRA</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>BRU-BGR</t>
+          <t>PMI-BHX</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>KIR-HHN</t>
+          <t>LIG-MAN</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>SFO-ORY</t>
+          <t>GLA-FCO</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>AMS-BGI</t>
+          <t>BRU-BGR</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>DUB-CCF</t>
+          <t>SFO-ORY</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>MUC-LAX</t>
+          <t>LHR-BWI</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>LPL-LGW</t>
+          <t>BHX-OPO</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>DUB-PRG</t>
+          <t>ATL-DOH</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>LEJ-CVG</t>
+          <t>DUS-LCA</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>EMA-CIA</t>
+          <t>LTN-KIR</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>SEA-FRA</t>
+          <t>BOS-DXB</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>BGO-LPA</t>
+          <t>EMA-CIA</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>BOS-DXB</t>
+          <t>NAP-EWR</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>STR-LHR</t>
+          <t>BGO-LPA</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>LTN-KIR</t>
+          <t>SEA-FRA</t>
         </is>
       </c>
       <c r="C893" t="n">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>SOU-MAN</t>
+          <t>LEJ-CVG</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>TRN-DUB</t>
+          <t>SOU-MAN</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>DUS-LCA</t>
+          <t>TRN-DUB</t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>EMA-FUE</t>
+          <t>DUB-CCF</t>
         </is>
       </c>
       <c r="C897" t="n">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>NAP-EWR</t>
+          <t>EMA-FUE</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>BHX-OPO</t>
+          <t>AMS-BGI</t>
         </is>
       </c>
       <c r="C899" t="n">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>LHR-BWI</t>
+          <t>WAW-MIA</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -12133,11 +12133,11 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>IAH-IST</t>
+          <t>FAO-LGW</t>
         </is>
       </c>
       <c r="C901" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="902">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>BRS-GDN</t>
+          <t>LCY-BHD</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>CUN-LGW</t>
+          <t>LGW-LIN</t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>LCY-BHD</t>
+          <t>CUN-LGW</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>LGW-LIN</t>
+          <t>LGW-MLA</t>
         </is>
       </c>
       <c r="C905" t="n">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>FAO-LGW</t>
+          <t>AMS-PUJ</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>LGW-MLA</t>
+          <t>LHR-TLV</t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>LPL-BVA</t>
+          <t>PUJ-WAW</t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>CGN-CVG</t>
+          <t>ATL-IST</t>
         </is>
       </c>
       <c r="C909" t="n">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>LGW-ARN</t>
+          <t>LHR-ADD</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>NCL-FAB</t>
+          <t>EWR-ZRH</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>AMS-PUJ</t>
+          <t>NCL-FAB</t>
         </is>
       </c>
       <c r="C912" t="n">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>LHR-TLV</t>
+          <t>CGN-CVG</t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>ATL-IST</t>
+          <t>LGW-ARN</t>
         </is>
       </c>
       <c r="C914" t="n">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>LHR-ADD</t>
+          <t>LPL-BVA</t>
         </is>
       </c>
       <c r="C915" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>EWR-ZRH</t>
+          <t>BRS-GDN</t>
         </is>
       </c>
       <c r="C916" t="n">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>PUJ-WAW</t>
+          <t>LGW-BGI</t>
         </is>
       </c>
       <c r="C917" t="n">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>LGW-BGI</t>
+          <t>INV-MAN</t>
         </is>
       </c>
       <c r="C918" t="n">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>INV-MAN</t>
+          <t>MAN-INN</t>
         </is>
       </c>
       <c r="C919" t="n">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>DXB-YYZ</t>
+          <t>PSA-MAN</t>
         </is>
       </c>
       <c r="C920" t="n">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>STN-SDF</t>
+          <t>CDG-KEF</t>
         </is>
       </c>
       <c r="C921" t="n">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>PSA-MAN</t>
+          <t>LGW-FUE</t>
         </is>
       </c>
       <c r="C922" t="n">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>CDG-KEF</t>
+          <t>LGG-RFD</t>
         </is>
       </c>
       <c r="C923" t="n">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>LGW-FUE</t>
+          <t>LHR-ZAG</t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>LGG-RFD</t>
+          <t>FRA-MBJ</t>
         </is>
       </c>
       <c r="C925" t="n">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>LHR-ZAG</t>
+          <t>MUC-ORK</t>
         </is>
       </c>
       <c r="C926" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>FRA-MBJ</t>
+          <t>MAN-TSF</t>
         </is>
       </c>
       <c r="C927" t="n">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>MUC-ORK</t>
+          <t>EMA-BGY</t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>MAN-TSF</t>
+          <t>DUB-DXB</t>
         </is>
       </c>
       <c r="C929" t="n">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>EMA-BGY</t>
+          <t>DUS-LRM</t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>DUB-DXB</t>
+          <t>KEF-LGG</t>
         </is>
       </c>
       <c r="C931" t="n">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>DUS-LRM</t>
+          <t>MAN-CPH</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>MAN-CPH</t>
+          <t>DUB-TSF</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>DUB-TSF</t>
+          <t>MIA-MUC</t>
         </is>
       </c>
       <c r="C934" t="n">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>MIA-MUC</t>
+          <t>BGY-NOC</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>BGY-NOC</t>
+          <t>KTW-CUN</t>
         </is>
       </c>
       <c r="C936" t="n">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>KTW-CUN</t>
+          <t>STN-SDF</t>
         </is>
       </c>
       <c r="C937" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>MAN-INN</t>
+          <t>STR-LGW</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>STR-LGW</t>
+          <t>DXB-YYZ</t>
         </is>
       </c>
       <c r="C939" t="n">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>BUD-MAN</t>
+          <t>AMS-DUB</t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>AMS-DUB</t>
+          <t>DXB-MAN</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>DXB-MAN</t>
+          <t>MLA-LHR</t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>MLA-LHR</t>
+          <t>MAN-DOH</t>
         </is>
       </c>
       <c r="C944" t="n">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>MAN-DOH</t>
+          <t>ZRH-LGW</t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>ZRH-LGW</t>
+          <t>MUC-MAN</t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>MUC-MAN</t>
+          <t>MAN-BHD</t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>MAN-BHD</t>
+          <t>BUD-MAN</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>LHR-LAS</t>
+          <t>LHR-INV</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>LHR-INV</t>
+          <t>OTP-LHR</t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>OTP-LHR</t>
+          <t>VIE-CUN</t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>VIE-CUN</t>
+          <t>DUB-IST</t>
         </is>
       </c>
       <c r="C953" t="n">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>DUB-IST</t>
+          <t>DXB-IAH</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>DXB-IAH</t>
+          <t>CUN-VIE</t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>CUN-VIE</t>
+          <t>OPO-LHR</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>OPO-LHR</t>
+          <t>LHR-LAS</t>
         </is>
       </c>
       <c r="C957" t="n">

--- a/aircraft/reports/top-routes-unidirectional.xlsx
+++ b/aircraft/reports/top-routes-unidirectional.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZRH-EWR</t>
+          <t>NCL-PMI</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NCL-PMI</t>
+          <t>ZRH-EWR</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MUC-YYZ</t>
+          <t>BCN-MAN</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BCN-MAN</t>
+          <t>MUC-YYZ</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CDG-JFK</t>
+          <t>BRU-MIA</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BRU-MIA</t>
+          <t>CDG-JFK</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EDI-GVA</t>
+          <t>GYE-AMS</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GYE-AMS</t>
+          <t>EDI-GVA</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CDG-LAX</t>
+          <t>MUC-ORD</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MUC-ORD</t>
+          <t>CDG-LAX</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GRU-AMS</t>
+          <t>PMI-MAN</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PMI-MAN</t>
+          <t>GRU-AMS</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BRS-AMS</t>
+          <t>LGG-MEM</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LGG-MEM</t>
+          <t>BRS-AMS</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MUC-CLT</t>
+          <t>IST-DUB</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EDI-PMI</t>
+          <t>MUC-EWR</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IST-DUB</t>
+          <t>MUC-CLT</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FRA-IAH</t>
+          <t>MUC-IAD</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MUC-IAD</t>
+          <t>MAN-MLA</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MAN-MLA</t>
+          <t>FRA-IAH</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MUC-EWR</t>
+          <t>EDI-PMI</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EWR-FRA</t>
+          <t>MUC-JFK</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MUC-JFK</t>
+          <t>EWR-FRA</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1551,11 +1551,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ORK-AMS</t>
+          <t>JFK-LHR</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88">
@@ -1564,11 +1564,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CDG-YUL</t>
+          <t>ORK-AMS</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FRA-CUN</t>
+          <t>CDG-YUL</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EWR-MUC</t>
+          <t>FRA-CUN</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FRA-DFW</t>
+          <t>EWR-MUC</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ATH-LCA</t>
+          <t>FRA-DFW</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ORD-MUC</t>
+          <t>ATH-LCA</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LBA-ALC</t>
+          <t>ORD-MUC</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MUC-YUL</t>
+          <t>LBA-ALC</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FRA-MIA</t>
+          <t>MUC-YUL</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IST-JFK</t>
+          <t>FRA-MIA</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JFK-LHR</t>
+          <t>IST-JFK</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MAN-REU</t>
+          <t>NCL-IBZ</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ISL-SNN</t>
+          <t>MAN-REU</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LGW-RMU</t>
+          <t>ISL-SNN</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>AMS-UIO</t>
+          <t>LGW-RMU</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>BHX-AGP</t>
+          <t>AMS-UIO</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MAN-LHR</t>
+          <t>BHX-AGP</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ZRH-YYZ</t>
+          <t>MAN-LHR</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SFO-FRA</t>
+          <t>ZRH-YYZ</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3007,11 +3007,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>NCL-IBZ</t>
+          <t>SFO-FRA</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DFW-LUX</t>
+          <t>PIK-PMI</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>BRU-CVG</t>
+          <t>DFW-LUX</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DFW-FRA</t>
+          <t>BRU-CVG</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>LHR-IST</t>
+          <t>DFW-FRA</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PIK-PMI</t>
+          <t>BHX-GVA</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>GCI-EMA</t>
+          <t>LHR-IST</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BHX-GVA</t>
+          <t>GCI-EMA</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>LHR-YYZ</t>
+          <t>EMA-GCI</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EMA-GCI</t>
+          <t>LHR-YYZ</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>AMS-YYZ</t>
+          <t>MUC-ATL</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>LIS-LHR</t>
+          <t>AMS-YYZ</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>LHR-LCA</t>
+          <t>LIS-LHR</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MUC-ATL</t>
+          <t>LHR-LCA</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PMI-LBA</t>
+          <t>YYZ-MUC</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YYZ-MUC</t>
+          <t>PMI-LBA</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>LHR-ATH</t>
+          <t>FRA-LCA</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>LHR-BRU</t>
+          <t>AGP-LGW</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>YYZ-LGW</t>
+          <t>YYC-CDG</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>JFK-DXB</t>
+          <t>YYZ-LGW</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>YYC-CDG</t>
+          <t>DXB-JFK</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>DXB-JFK</t>
+          <t>JFK-DXB</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>ZAG-DUB</t>
+          <t>LHR-ZRH</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>BRU-CUN</t>
+          <t>ZAG-DUB</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>LHR-ZRH</t>
+          <t>LHR-BRU</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>LPL-IBZ</t>
+          <t>VIE-LCA</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>FRA-LCA</t>
+          <t>BRU-CUN</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>SKG-LCA</t>
+          <t>LPL-IBZ</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>VIE-LCA</t>
+          <t>ALC-LGW</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>ALC-LGW</t>
+          <t>LIN-LHR</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>LIN-LHR</t>
+          <t>IST-YUL</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>IST-YUL</t>
+          <t>LHR-ARN</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>ATH-DUB</t>
+          <t>GVA-LGW</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>GVA-LGW</t>
+          <t>SKG-LCA</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>AGP-LGW</t>
+          <t>EWR-LHR</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>LHR-ARN</t>
+          <t>IAH-LHR</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>EWR-LHR</t>
+          <t>DUB-CIA</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>CRL-ORK</t>
+          <t>BQN-AMS</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>OSL-LHR</t>
+          <t>GLA-SOU</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>DUB-CIA</t>
+          <t>LHR-ATH</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>BQN-AMS</t>
+          <t>VCE-LGW</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>YYC-LGW</t>
+          <t>LBA-CDG</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>BOS-FRA</t>
+          <t>BGY-DUB</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>IAH-LHR</t>
+          <t>CPH-LGW</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>AMM-JFK</t>
+          <t>BOS-FRA</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>LBA-CDG</t>
+          <t>YYC-LGW</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>BGY-DUB</t>
+          <t>AMM-JFK</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>CPH-LGW</t>
+          <t>OSL-LHR</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>GLA-SOU</t>
+          <t>CRL-ORK</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>VCE-LGW</t>
+          <t>ATH-DUB</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EMA-LPA</t>
+          <t>BHX-FCO</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>MAD-MAN</t>
+          <t>PVG-LHR</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>PVG-LHR</t>
+          <t>MAD-MAN</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>BHX-FCO</t>
+          <t>EMA-LPA</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>BOM-LHR</t>
+          <t>YYZ-IST</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>LCK-LUX</t>
+          <t>JER-LGW</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>EDI-ORY</t>
+          <t>VIE-YUL</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PHL-CGN</t>
+          <t>EDI-ORY</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>VIE-YUL</t>
+          <t>PHL-CGN</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>LHR-HAM</t>
+          <t>MAN-VLC</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>MRS-DUB</t>
+          <t>LHR-HAM</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>MAN-VLC</t>
+          <t>MRS-DUB</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>AMS-MEX</t>
+          <t>BOM-LHR</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>YYZ-IST</t>
+          <t>AMS-MEX</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>JER-LGW</t>
+          <t>PTY-LGG</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>BHX-FUE</t>
+          <t>LHR-SFO</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>CPH-LCA</t>
+          <t>MAN-BSL</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>ZRH-YUL</t>
+          <t>CDG-MAN</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>HSV-LUX</t>
+          <t>BOS-MUC</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>IAD-IST</t>
+          <t>BHX-MAH</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>JFK-AMS</t>
+          <t>EDI-CRL</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>JER-MAN</t>
+          <t>LHR-CPH</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>LHR-CPH</t>
+          <t>LHR-ABZ</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>EDI-CRL</t>
+          <t>GCI-MAN</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>MAN-BSL</t>
+          <t>BHX-FNC</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>BHX-FNC</t>
+          <t>HSV-LUX</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>LHR-FCO</t>
+          <t>ZRH-YUL</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>BHX-MAH</t>
+          <t>IAD-IST</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>BOS-MUC</t>
+          <t>JFK-AMS</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>PTY-LGG</t>
+          <t>JER-MAN</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>LHR-SFO</t>
+          <t>BHX-FUE</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>FCO-LHR</t>
+          <t>LHR-FCO</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>IST-ATL</t>
+          <t>CPH-LCA</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>CDG-MAN</t>
+          <t>FCO-LHR</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>BRU-LHR</t>
+          <t>IST-ATL</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>LHR-DUS</t>
+          <t>BRU-LHR</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>LHR-HEL</t>
+          <t>LCK-LUX</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>GCI-MAN</t>
+          <t>LHR-DUS</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -6517,11 +6517,11 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>MAN-JED</t>
+          <t>LHR-HEL</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="470">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>GSP-FRA</t>
+          <t>BHX-LCA</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>ZRH-SFO</t>
+          <t>PUJ-FRA</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>BUD-LGW</t>
+          <t>NAP-DUB</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>MAD-LGW</t>
+          <t>MAN-HER</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>ZRH-PHL</t>
+          <t>GSP-FRA</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>MAN-HER</t>
+          <t>CEG-TLS</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>LAS-LGW</t>
+          <t>JFK-CDG</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>DFW-DOH</t>
+          <t>BCN-LHR</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>LGG-IND</t>
+          <t>ZRH-SFO</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>GCI-BHX</t>
+          <t>MAN-JED</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>MAN-CTA</t>
+          <t>BUD-LGW</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>CEG-TLS</t>
+          <t>MAD-LGW</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>JFK-CDG</t>
+          <t>LGG-IND</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>BCN-LHR</t>
+          <t>IAD-LHR</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>NAP-DUB</t>
+          <t>ZRH-PHL</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>BRS-POZ</t>
+          <t>MST-ATL</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>MST-ATL</t>
+          <t>BRS-POZ</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>IAD-LHR</t>
+          <t>JER-EMA</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>JER-EMA</t>
+          <t>GCI-BHX</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>BHX-LCA</t>
+          <t>DFW-DOH</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>PUJ-FRA</t>
+          <t>LAS-LGW</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>BEG-LCA</t>
+          <t>MAN-CTA</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>DUB-VCE</t>
+          <t>BEG-LCA</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MAN-LEI</t>
+          <t>DUB-VCE</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>YUL-FRA</t>
+          <t>MAN-LEI</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>WRT-FAB</t>
+          <t>DEL-LHR</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>LHR-VCE</t>
+          <t>WRT-FAB</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>BER-LHR</t>
+          <t>LHR-VCE</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>DXB-BOS</t>
+          <t>BER-LHR</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>ORD-ZRH</t>
+          <t>DXB-BOS</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>ZRH-BOS</t>
+          <t>ORD-ZRH</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>EMA-JER</t>
+          <t>ZRH-BOS</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>GLA-LHR</t>
+          <t>EMA-JER</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>BHD-LHR</t>
+          <t>GLA-LHR</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>TPA-FRA</t>
+          <t>BHD-LHR</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>DUB-LIN</t>
+          <t>TPA-FRA</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>IST-IAH</t>
+          <t>DUB-LIN</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>DEL-LHR</t>
+          <t>YUL-FRA</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>ABZ-ALC</t>
+          <t>IST-IAH</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>MAN-GCI</t>
+          <t>ABZ-ALC</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>MAN-AYT</t>
+          <t>MAN-GCI</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>ABZ-LHR</t>
+          <t>MAN-AYT</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>DOH-LHR</t>
+          <t>ABZ-LHR</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>LHR-ABZ</t>
+          <t>DOH-LHR</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>BHX-GCI</t>
+          <t>CDG-LGW</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>LIN-DUB</t>
+          <t>FRA-ORK</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>NCL-MAH</t>
+          <t>POZ-ORK</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>IBZ-EDI</t>
+          <t>GLA-BCN</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>BHX-RHO</t>
+          <t>SJO-FRA</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>CDG-LGW</t>
+          <t>EWR-DEL</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>CRL-DUB</t>
+          <t>MIA-LGG</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>EWR-DEL</t>
+          <t>BHX-GCI</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>SJO-FRA</t>
+          <t>LIN-DUB</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>GLA-BCN</t>
+          <t>NCL-MAH</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>POZ-ORK</t>
+          <t>IBZ-EDI</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>JFK-MXP</t>
+          <t>BHX-RHO</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>REU-GLA</t>
+          <t>LGW-AMS</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>BRS-WRO</t>
+          <t>CDG-MSP</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>SFO-ZRH</t>
+          <t>BUD-SNN</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>BUD-SNN</t>
+          <t>CRL-DUB</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>FRA-ORK</t>
+          <t>JFK-MXP</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>CDG-MSP</t>
+          <t>REU-GLA</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>LGW-AMS</t>
+          <t>SFO-ZRH</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MIA-LGG</t>
+          <t>BRS-WRO</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>LUX-ORD</t>
+          <t>CDG-YVR</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>KRK-SNN</t>
+          <t>LUX-ORD</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>BRS-WMI</t>
+          <t>RUH-IAD</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>DTW-CDG</t>
+          <t>BRS-WMI</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>CDG-YVR</t>
+          <t>DUB-BLQ</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>LUX-ATL</t>
+          <t>STN-KIR</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>STN-KIR</t>
+          <t>DTW-CDG</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>DUB-BLQ</t>
+          <t>KRK-SNN</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>RUH-IAD</t>
+          <t>LUX-ATL</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>AGP-EDI</t>
+          <t>ORD-HHN</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>IAH-DXB</t>
+          <t>AGP-EDI</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>DUB-TRN</t>
+          <t>IAH-DXB</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>LGW-PMI</t>
+          <t>DUB-TRN</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>HUY-PMI</t>
+          <t>LGW-PMI</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>ATH-JFK</t>
+          <t>KEF-LGG</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>PSA-DUB</t>
+          <t>ATH-JFK</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>TLV-LHR</t>
+          <t>PSA-DUB</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>ORD-HHN</t>
+          <t>TLV-LHR</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>WAW-PUJ</t>
+          <t>HUY-PMI</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>MUC-LAX</t>
+          <t>WAW-PUJ</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>ORD-AMM</t>
+          <t>BRS-ALC</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>MAN-DXB</t>
+          <t>ORD-AMM</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>BRS-ALC</t>
+          <t>MAN-DXB</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>LCA-BEG</t>
+          <t>ARN-LPA</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>ARN-LPA</t>
+          <t>LCA-BEG</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>LCA-WAW</t>
+          <t>PHL-LHR</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>LCA-CPH</t>
+          <t>LCA-WAW</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>PHL-LHR</t>
+          <t>LCA-CPH</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>DUB-PRG</t>
+          <t>HHN-RFD</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>AGP-BHX</t>
+          <t>ATL-DOH</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>FRA-NLU</t>
+          <t>YUL-DOH</t>
         </is>
       </c>
       <c r="C837" t="n">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>YUL-DOH</t>
+          <t>FRA-NLU</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>ATH-YUL</t>
+          <t>TFS-LGW</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>ATL-MUC</t>
+          <t>ATH-YUL</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>DXB-EWR</t>
+          <t>ATL-MUC</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>LBA-GRO</t>
+          <t>DXB-EWR</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>LHR-SEA</t>
+          <t>LBA-GRO</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>MAN-VRN</t>
+          <t>LHR-SEA</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>MAN-LYS</t>
+          <t>MAN-VRN</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>OST-JFK</t>
+          <t>MAN-LYS</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>TFS-LGW</t>
+          <t>OST-JFK</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>JED-YYZ</t>
+          <t>LHR-HKG</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>MAN-GNB</t>
+          <t>JED-YYZ</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>BRS-BZG</t>
+          <t>MAN-GNB</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>ATL-ISL</t>
+          <t>BRS-BZG</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>LHR-HKG</t>
+          <t>ATL-ISL</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>MAN-DUB</t>
+          <t>NTE-EDI</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>MAN-SOU</t>
+          <t>MAN-DUB</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>DUB-MRS</t>
+          <t>MAN-SOU</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>NTE-EDI</t>
+          <t>DUB-MRS</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>HHN-RFD</t>
+          <t>AGP-BHX</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>FRA-RDU</t>
+          <t>LIG-MAN</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>STR-LHR</t>
+          <t>CDG-LCA</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>IAH-IST</t>
+          <t>JTR-LHR</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>ORK-GDN</t>
+          <t>LTN-CDG</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>LPL-LGW</t>
+          <t>NTE-MAN</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>CDG-LCA</t>
+          <t>MXP-LHR</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>JTR-LHR</t>
+          <t>VIE-BOS</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>KIR-HHN</t>
+          <t>PHL-DOH</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>NTE-MAN</t>
+          <t>YYC-FRA</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>MXP-LHR</t>
+          <t>PMI-BHX</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>LTN-CDG</t>
+          <t>GLA-FCO</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>LCY-AMS</t>
+          <t>ORK-GDN</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>VIE-BOS</t>
+          <t>WAW-MIA</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>PHL-DOH</t>
+          <t>LCY-AMS</t>
         </is>
       </c>
       <c r="C877" t="n">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>YYC-FRA</t>
+          <t>FRA-RDU</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>PMI-BHX</t>
+          <t>BRU-BGR</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>LIG-MAN</t>
+          <t>KIR-HHN</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>GLA-FCO</t>
+          <t>SFO-ORY</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>BRU-BGR</t>
+          <t>AMS-BGI</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>SFO-ORY</t>
+          <t>DUB-CCF</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>LHR-BWI</t>
+          <t>MUC-LAX</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>BHX-OPO</t>
+          <t>LPL-LGW</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>ATL-DOH</t>
+          <t>DUB-PRG</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>DUS-LCA</t>
+          <t>LEJ-CVG</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>LTN-KIR</t>
+          <t>EMA-CIA</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>BOS-DXB</t>
+          <t>SEA-FRA</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>EMA-CIA</t>
+          <t>BGO-LPA</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>NAP-EWR</t>
+          <t>BOS-DXB</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>BGO-LPA</t>
+          <t>STR-LHR</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>SEA-FRA</t>
+          <t>LTN-KIR</t>
         </is>
       </c>
       <c r="C893" t="n">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>LEJ-CVG</t>
+          <t>SOU-MAN</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>SOU-MAN</t>
+          <t>TRN-DUB</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>TRN-DUB</t>
+          <t>DUS-LCA</t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>DUB-CCF</t>
+          <t>EMA-FUE</t>
         </is>
       </c>
       <c r="C897" t="n">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>EMA-FUE</t>
+          <t>NAP-EWR</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>AMS-BGI</t>
+          <t>BHX-OPO</t>
         </is>
       </c>
       <c r="C899" t="n">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>WAW-MIA</t>
+          <t>LHR-BWI</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -12133,11 +12133,11 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>FAO-LGW</t>
+          <t>IAH-IST</t>
         </is>
       </c>
       <c r="C901" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="902">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>LCY-BHD</t>
+          <t>BRS-GDN</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>LGW-LIN</t>
+          <t>CUN-LGW</t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>CUN-LGW</t>
+          <t>LCY-BHD</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>LGW-MLA</t>
+          <t>LGW-LIN</t>
         </is>
       </c>
       <c r="C905" t="n">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>AMS-PUJ</t>
+          <t>FAO-LGW</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>LHR-TLV</t>
+          <t>LGW-MLA</t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>PUJ-WAW</t>
+          <t>LPL-BVA</t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>ATL-IST</t>
+          <t>CGN-CVG</t>
         </is>
       </c>
       <c r="C909" t="n">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>LHR-ADD</t>
+          <t>LGW-ARN</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>EWR-ZRH</t>
+          <t>NCL-FAB</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>NCL-FAB</t>
+          <t>AMS-PUJ</t>
         </is>
       </c>
       <c r="C912" t="n">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>CGN-CVG</t>
+          <t>LHR-TLV</t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>LGW-ARN</t>
+          <t>ATL-IST</t>
         </is>
       </c>
       <c r="C914" t="n">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>LPL-BVA</t>
+          <t>LHR-ADD</t>
         </is>
       </c>
       <c r="C915" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>BRS-GDN</t>
+          <t>EWR-ZRH</t>
         </is>
       </c>
       <c r="C916" t="n">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>LGW-BGI</t>
+          <t>PUJ-WAW</t>
         </is>
       </c>
       <c r="C917" t="n">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>INV-MAN</t>
+          <t>LGW-BGI</t>
         </is>
       </c>
       <c r="C918" t="n">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>MAN-INN</t>
+          <t>INV-MAN</t>
         </is>
       </c>
       <c r="C919" t="n">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>PSA-MAN</t>
+          <t>DXB-YYZ</t>
         </is>
       </c>
       <c r="C920" t="n">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>CDG-KEF</t>
+          <t>STN-SDF</t>
         </is>
       </c>
       <c r="C921" t="n">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>LGW-FUE</t>
+          <t>PSA-MAN</t>
         </is>
       </c>
       <c r="C922" t="n">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>LGG-RFD</t>
+          <t>CDG-KEF</t>
         </is>
       </c>
       <c r="C923" t="n">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>LHR-ZAG</t>
+          <t>LGW-FUE</t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>FRA-MBJ</t>
+          <t>LGG-RFD</t>
         </is>
       </c>
       <c r="C925" t="n">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>MUC-ORK</t>
+          <t>LHR-ZAG</t>
         </is>
       </c>
       <c r="C926" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>MAN-TSF</t>
+          <t>FRA-MBJ</t>
         </is>
       </c>
       <c r="C927" t="n">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>EMA-BGY</t>
+          <t>MUC-ORK</t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>DUB-DXB</t>
+          <t>MAN-TSF</t>
         </is>
       </c>
       <c r="C929" t="n">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>DUS-LRM</t>
+          <t>EMA-BGY</t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>KEF-LGG</t>
+          <t>DUB-DXB</t>
         </is>
       </c>
       <c r="C931" t="n">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>MAN-CPH</t>
+          <t>DUS-LRM</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>DUB-TSF</t>
+          <t>MAN-CPH</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>MIA-MUC</t>
+          <t>DUB-TSF</t>
         </is>
       </c>
       <c r="C934" t="n">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>BGY-NOC</t>
+          <t>MIA-MUC</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>KTW-CUN</t>
+          <t>BGY-NOC</t>
         </is>
       </c>
       <c r="C936" t="n">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>STN-SDF</t>
+          <t>KTW-CUN</t>
         </is>
       </c>
       <c r="C937" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>STR-LGW</t>
+          <t>MAN-INN</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>DXB-YYZ</t>
+          <t>STR-LGW</t>
         </is>
       </c>
       <c r="C939" t="n">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>AMS-DUB</t>
+          <t>BUD-MAN</t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>DXB-MAN</t>
+          <t>AMS-DUB</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>MLA-LHR</t>
+          <t>DXB-MAN</t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>MAN-DOH</t>
+          <t>MLA-LHR</t>
         </is>
       </c>
       <c r="C944" t="n">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>ZRH-LGW</t>
+          <t>MAN-DOH</t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>MUC-MAN</t>
+          <t>ZRH-LGW</t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>MAN-BHD</t>
+          <t>MUC-MAN</t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>BUD-MAN</t>
+          <t>MAN-BHD</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>LHR-INV</t>
+          <t>LHR-LAS</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>OTP-LHR</t>
+          <t>LHR-INV</t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>VIE-CUN</t>
+          <t>OTP-LHR</t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>DUB-IST</t>
+          <t>VIE-CUN</t>
         </is>
       </c>
       <c r="C953" t="n">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>DXB-IAH</t>
+          <t>DUB-IST</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>CUN-VIE</t>
+          <t>DXB-IAH</t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>OPO-LHR</t>
+          <t>CUN-VIE</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>LHR-LAS</t>
+          <t>OPO-LHR</t>
         </is>
       </c>
       <c r="C957" t="n">

--- a/aircraft/reports/top-routes-unidirectional.xlsx
+++ b/aircraft/reports/top-routes-unidirectional.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FRA-EWR</t>
+          <t>EDI-CDG</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EDI-CDG</t>
+          <t>FRA-EWR</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -732,11 +732,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CUR-AMS</t>
+          <t>MAN-BCN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
@@ -745,7 +745,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAN-BCN</t>
+          <t>CUR-AMS</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AMS-ATL</t>
+          <t>MAN-IBZ</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FRA-BOS</t>
+          <t>AMS-ATL</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CDG-DUB</t>
+          <t>FRA-BOS</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1018,11 +1018,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MAN-IBZ</t>
+          <t>CDG-DUB</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MAN-MLA</t>
+          <t>LPL-PMI</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MUC-EWR</t>
+          <t>MAN-MLA</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EDI-PMI</t>
+          <t>MUC-EWR</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FRA-IAH</t>
+          <t>EDI-PMI</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MUC-CLT</t>
+          <t>FRA-IAH</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IST-DUB</t>
+          <t>MUC-CLT</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1499,11 +1499,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LPL-PMI</t>
+          <t>IST-DUB</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MUC-JFK</t>
+          <t>ORK-AMS</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EWR-FRA</t>
+          <t>MUC-JFK</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JFK-LHR</t>
+          <t>EWR-FRA</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1564,11 +1564,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ORK-AMS</t>
+          <t>JFK-LHR</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CDG-ATL</t>
+          <t>BHD-LGW</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GVA-DUB</t>
+          <t>CDG-ATL</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NCL-ALC</t>
+          <t>GVA-DUB</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2149,11 +2149,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CUN-FRA</t>
+          <t>NCL-ALC</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BHD-LGW</t>
+          <t>CUN-FRA</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AMS-BON</t>
+          <t>PMI-GLA</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CDG-ORD</t>
+          <t>AMS-BON</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EMA-AGP</t>
+          <t>CDG-ORD</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LGG-ORD</t>
+          <t>MAN-MAH</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PMI-GLA</t>
+          <t>LGG-ORD</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2565,11 +2565,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DXB-DUB</t>
+          <t>EMA-AGP</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MAN-RMU</t>
+          <t>AMS-ORD</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EMA-PMI</t>
+          <t>MAN-RMU</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>AMS-ORD</t>
+          <t>DXB-DUB</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ZRH-LHR</t>
+          <t>EMA-PMI</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MAD-LHR</t>
+          <t>NCL-IBZ</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BCN-EDI</t>
+          <t>MAD-LHR</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HHN-GSP</t>
+          <t>BCN-EDI</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>BHX-FAO</t>
+          <t>HHN-GSP</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EMA-TFS</t>
+          <t>BHX-FAO</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>GLA-ALC</t>
+          <t>EMA-TFS</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TLV-EWR</t>
+          <t>GLA-ALC</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EMA-FAO</t>
+          <t>ZRH-LHR</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>BFS-CDG</t>
+          <t>ALC-EDI</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MAN-MAH</t>
+          <t>TLV-EWR</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ALC-EDI</t>
+          <t>BFS-CDG</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -2851,11 +2851,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NCL-IBZ</t>
+          <t>EMA-FAO</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="188">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FRA-PHL</t>
+          <t>ZRH-YYZ</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LHR-ORD</t>
+          <t>CDG-YYZ</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PBM-AMS</t>
+          <t>AMS-UIO</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CDG-YYZ</t>
+          <t>LHR-ORD</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>AMS-UIO</t>
+          <t>PBM-AMS</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ZRH-YYZ</t>
+          <t>FRA-PHL</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>AMS-PHL</t>
+          <t>LHR-YYZ</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>LHR-YYZ</t>
+          <t>AMS-PHL</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>EDI-IBZ</t>
+          <t>DOH-ORD</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>EWR-TLV</t>
+          <t>MEX-FRA</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>KWI-JFK</t>
+          <t>VCE-DUB</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>VCE-DUB</t>
+          <t>KWI-JFK</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>FRA-YHZ</t>
+          <t>LHR-CDG</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>LHR-CDG</t>
+          <t>FRA-YHZ</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DOH-ORD</t>
+          <t>EDI-IBZ</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>MEX-FRA</t>
+          <t>EWR-TLV</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>TLV-LCA</t>
+          <t>BHX-ACE</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>YUL-CDG</t>
+          <t>TLV-LCA</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>LHR-IAD</t>
+          <t>YUL-CDG</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>FRA-MEX</t>
+          <t>LHR-IAD</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>GLA-CDG</t>
+          <t>FRA-MEX</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -3514,11 +3514,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>LHR-MAN</t>
+          <t>GLA-CDG</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="239">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>GVA-LHR</t>
+          <t>LHR-MAN</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>LGW-ALC</t>
+          <t>GVA-LHR</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>BHX-ACE</t>
+          <t>LGW-ALC</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>BHX-TFS</t>
+          <t>GSP-HHN</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>GSP-HHN</t>
+          <t>LAX-LHR</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>LAX-LHR</t>
+          <t>BHX-TFS</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>JFK-TLV</t>
+          <t>DOH-JFK</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>DOH-JFK</t>
+          <t>JFK-TLV</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>LHR-MAD</t>
+          <t>LHR-LAX</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>LBA-IBZ</t>
+          <t>DUB-FRA</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DUB-FRA</t>
+          <t>LBA-IBZ</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>LHR-LAX</t>
+          <t>LHR-MAD</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>ALC-LBA</t>
+          <t>LPL-NCE</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>IST-LHR</t>
+          <t>ALC-LBA</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>BOS-LHR</t>
+          <t>IST-LHR</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DOH-DUB</t>
+          <t>BOS-LHR</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>LHR-FRA</t>
+          <t>DOH-DUB</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>AUH-IAD</t>
+          <t>LHR-FRA</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>LCA-ATH</t>
+          <t>AUH-IAD</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>LCA-LHR</t>
+          <t>LCA-ATH</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>MAN-BGY</t>
+          <t>LCA-LHR</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>AMS-IAH</t>
+          <t>MAN-BGY</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CDG-LHR</t>
+          <t>AMS-IAH</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>LGW-BCN</t>
+          <t>CDG-LHR</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>MAN-PSA</t>
+          <t>CDG-BOS</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>RMU-LGW</t>
+          <t>LGW-BCN</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>CDG-BOS</t>
+          <t>RMU-LGW</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>STN-SNN</t>
+          <t>MAN-PSA</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>LHR-DOH</t>
+          <t>STN-SNN</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>YYZ-CDG</t>
+          <t>LHR-DOH</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4164,11 +4164,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>LPL-NCE</t>
+          <t>YYZ-CDG</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MUC-LHR</t>
+          <t>MCO-FRA</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>WRO-SNN</t>
+          <t>IND-CGN</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MAN-GRO</t>
+          <t>NCE-LHR</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>AMS-LGW</t>
+          <t>HND-LHR</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SFO-LHR</t>
+          <t>BCN-LGW</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ATH-LHR</t>
+          <t>YUL-MUC</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>MXP-JFK</t>
+          <t>DOH-IAD</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DXB-LHR</t>
+          <t>MAN-GRO</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>IND-CGN</t>
+          <t>WRO-SNN</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>NCE-LHR</t>
+          <t>YHZ-LGG</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>HND-LHR</t>
+          <t>AMS-LGW</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>YHZ-LGG</t>
+          <t>ATH-LHR</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>FMM-DUB</t>
+          <t>DXB-LHR</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>JER-BHX</t>
+          <t>MXP-JFK</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>IND-LUX</t>
+          <t>MUC-LHR</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>AMS-SJO</t>
+          <t>FMM-DUB</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>YUL-MUC</t>
+          <t>JER-BHX</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>LPL-GVA</t>
+          <t>LPL-JER</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>LYS-DUB</t>
+          <t>IND-LUX</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>BGR-LUX</t>
+          <t>KEF-LGW</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>KEF-LGW</t>
+          <t>BGR-LUX</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ALC-BHX</t>
+          <t>AMS-SJO</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>BCN-LGW</t>
+          <t>AMS-LIM</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>AMS-LIM</t>
+          <t>LYS-DUB</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DOH-IAD</t>
+          <t>LPL-GVA</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>MCO-FRA</t>
+          <t>SFO-LHR</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>LPL-JER</t>
+          <t>ALC-BHX</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>LHR-NCE</t>
+          <t>LHR-BCN</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>DUB-FCO</t>
+          <t>LAX-LUX</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>LAX-LUX</t>
+          <t>JFK-IST</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>SIN-LHR</t>
+          <t>LHR-NCE</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PIK-ALC</t>
+          <t>ORD-LHR</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>LHR-BCN</t>
+          <t>SIN-LHR</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>JFK-SIN</t>
+          <t>DUB-FCO</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>YVR-LGW</t>
+          <t>IST-YYZ</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>LCA-TLV</t>
+          <t>DOH-PHL</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>DOH-PHL</t>
+          <t>LCA-TLV</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>CDG-DFW</t>
+          <t>PIK-ALC</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>IST-YYZ</t>
+          <t>DUB-CGN</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DUB-CGN</t>
+          <t>AUH-JFK</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>CDG-SFO</t>
+          <t>SOU-BHD</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>SOU-BHD</t>
+          <t>JFK-SIN</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>LGG-ATL</t>
+          <t>CDG-DFW</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>AUH-JFK</t>
+          <t>CDG-SFO</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>ORD-IST</t>
+          <t>YVR-LGW</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>ORD-LHR</t>
+          <t>ORD-IST</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -4801,11 +4801,11 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>LHR-EDI</t>
+          <t>LGG-ATL</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="338">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>CDG-MEM</t>
+          <t>LAX-BRU</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>MAN-CGN</t>
+          <t>MIA-WAW</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>BHX-CDG</t>
+          <t>MEM-CDG</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>AMS-GIG</t>
+          <t>IAD-BRU</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>AMS-CUN</t>
+          <t>CDG-MEM</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ATH-EWR</t>
+          <t>MAN-JER</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>JFK-IST</t>
+          <t>BHX-LPA</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>MAN-JER</t>
+          <t>NRT-CDG</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>LBA-GVA</t>
+          <t>IOM-LGW</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>LAX-BRU</t>
+          <t>ATH-EWR</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>MUC-DEN</t>
+          <t>MAN-LGW</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>LHR-DFW</t>
+          <t>EDI-NCE</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>MEM-CDG</t>
+          <t>LBA-GVA</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>IOM-LGW</t>
+          <t>AMS-GIG</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>IAD-BRU</t>
+          <t>AMS-CUN</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>DUS-LHR</t>
+          <t>BHX-CDG</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>CAI-JFK</t>
+          <t>ATL-LGG</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>EDI-NCE</t>
+          <t>LHR-DFW</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>LHR-SIN</t>
+          <t>OSL-LPA</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>LHR-LIS</t>
+          <t>MEM-LGG</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>LHR-YVR</t>
+          <t>LHR-LIS</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>MEM-LGG</t>
+          <t>CWL-AMS</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>LHR-GLA</t>
+          <t>MAN-NAP</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>NRT-CDG</t>
+          <t>BFS-PMI</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>BFS-PMI</t>
+          <t>VIE-LHR</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>LHR-GVA</t>
+          <t>DUS-LHR</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>CPH-LHR</t>
+          <t>MAN-CGN</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>OSL-LPA</t>
+          <t>BGY-DUB</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>CWL-AMS</t>
+          <t>CAI-JFK</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MAN-NAP</t>
+          <t>LHR-YVR</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MIA-WAW</t>
+          <t>LHR-GLA</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ATL-LGG</t>
+          <t>LHR-GVA</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>MAN-LGW</t>
+          <t>MUC-DEN</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>VIE-LHR</t>
+          <t>LHR-EDI</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>DOH-YUL</t>
+          <t>LHR-SIN</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>BHX-LPA</t>
+          <t>CPH-LHR</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -5282,11 +5282,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>LPL-IBZ</t>
+          <t>DOH-YUL</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="375">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>ATH-DUB</t>
+          <t>LHR-ZRH</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>LHR-ZRH</t>
+          <t>EMA-ACE</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>CVG-LEJ</t>
+          <t>VCE-LGW</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ORD-AMS</t>
+          <t>CVG-LEJ</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>YYZ-LGW</t>
+          <t>LPL-IBZ</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>JFK-DXB</t>
+          <t>GLA-SOU</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>BOS-FRA</t>
+          <t>YYZ-DXB</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>GLA-SOU</t>
+          <t>CDG-MEX</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>BGY-DUB</t>
+          <t>LHR-ATH</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>CDG-MEX</t>
+          <t>ORD-AMS</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>IST-BOS</t>
+          <t>DUB-NCE</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>LHR-ATH</t>
+          <t>BOS-FRA</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>LHR-ARN</t>
+          <t>LHR-BRU</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>ALC-LGW</t>
+          <t>JFK-DXB</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>LHR-BRU</t>
+          <t>ALC-LGW</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>EWR-LHR</t>
+          <t>LHR-ARN</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>DUB-NCE</t>
+          <t>YYZ-LGW</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>CPH-LGW</t>
+          <t>EWR-LHR</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>VCE-LGW</t>
+          <t>ATH-DUB</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>ZAG-DUB</t>
+          <t>CPH-LGW</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>YYC-CDG</t>
+          <t>BRU-CUN</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>CRL-ORK</t>
+          <t>IST-BOS</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>SKG-LCA</t>
+          <t>DXB-JFK</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>YYZ-DXB</t>
+          <t>IST-YUL</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>VIE-LCA</t>
+          <t>FRA-LCA</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>EWR-BRU</t>
+          <t>LBA-CDG</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>IAH-LHR</t>
+          <t>CRL-ORK</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>BRU-CUN</t>
+          <t>OSL-LHR</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>LBA-CDG</t>
+          <t>EWR-BRU</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>IST-YUL</t>
+          <t>SKG-LCA</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>BQN-AMS</t>
+          <t>VIE-LCA</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>DUB-CIA</t>
+          <t>IAH-LHR</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>AMM-JFK</t>
+          <t>ZAG-DUB</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>OSL-LHR</t>
+          <t>BQN-AMS</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>GVA-LGW</t>
+          <t>DUB-CIA</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>FRA-LCA</t>
+          <t>AMM-JFK</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>BRU-ATL</t>
+          <t>YYC-CDG</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EMA-ACE</t>
+          <t>AMS-GRU</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>AGP-LGW</t>
+          <t>BRU-ATL</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>AMS-GRU</t>
+          <t>AGP-LGW</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>DXB-JFK</t>
+          <t>GVA-LGW</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>BRU-LHR</t>
+          <t>PHL-CGN</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>LIN-DUB</t>
+          <t>LHR-ABZ</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EWR-DEL</t>
+          <t>EDI-ORY</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>LHR-HAM</t>
+          <t>MAD-MAN</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>LHR-CPH</t>
+          <t>MRS-DUB</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>MAD-MAN</t>
+          <t>EMA-IBZ</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>MAN-VLC</t>
+          <t>HSV-LUX</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>LHR-ABZ</t>
+          <t>BRU-LHR</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>FCO-LHR</t>
+          <t>PTY-LGG</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>EMA-IBZ</t>
+          <t>FCO-LHR</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>HSV-LUX</t>
+          <t>BHX-FCO</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>LHR-HEL</t>
+          <t>LIN-DUB</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>LHR-SFO</t>
+          <t>EWR-DEL</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>AMS-MEX</t>
+          <t>LHR-HEL</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>VIE-YUL</t>
+          <t>LHR-CPH</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>BHX-FCO</t>
+          <t>LHR-HAM</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PTY-LGG</t>
+          <t>LAX-MUC</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>CDG-MAN</t>
+          <t>EDI-CRL</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>LAX-MUC</t>
+          <t>LHR-SFO</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>LHR-FCO</t>
+          <t>AMS-MEX</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>GCI-MAN</t>
+          <t>CDG-MAN</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>PHL-CGN</t>
+          <t>LHR-FCO</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>LHR-DUS</t>
+          <t>VIE-YUL</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>MRS-DUB</t>
+          <t>MAN-VLC</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>AMS-BRS</t>
+          <t>SOU-EDI</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>YYZ-IST</t>
+          <t>AMS-BRS</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SOU-EDI</t>
+          <t>YYZ-IST</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>DUB-MXP</t>
+          <t>GCI-MAN</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>EDI-CRL</t>
+          <t>LHR-DUS</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>EDI-ORY</t>
+          <t>DUB-MXP</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>EDI-BVA</t>
+          <t>MIA-LGG</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>MIA-LGG</t>
+          <t>NAP-DUB</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>NAP-DUB</t>
+          <t>EDI-BVA</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>BRS-KUN</t>
+          <t>GLA-REU</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>MAN-HER</t>
+          <t>BRS-KUN</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>LAS-LGW</t>
+          <t>MAN-HER</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>BHX-GCI</t>
+          <t>LAS-LGW</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>CRL-DUB</t>
+          <t>BHX-GCI</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -7466,11 +7466,11 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>DTW-CDG</t>
+          <t>CRL-DUB</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="543">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>YYZ-DOH</t>
+          <t>GLA-GVA</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>AGP-GLA</t>
+          <t>LTN-LCA</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>KEF-LHR</t>
+          <t>LCA-ZRH</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>ATL-CDG</t>
+          <t>BKK-LHR</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>GLA-REU</t>
+          <t>STN-KIR</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>MAN-TRN</t>
+          <t>ATL-CDG</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>VRA-FRA</t>
+          <t>BOS-DOH</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>MRU-CDG</t>
+          <t>BRU-VRA</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>LUX-ORD</t>
+          <t>MAN-TRN</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>BRU-VRA</t>
+          <t>LUX-ORD</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>MAN-DLM</t>
+          <t>MRU-CDG</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>LPL-CDG</t>
+          <t>VRA-FRA</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>BKK-LHR</t>
+          <t>LBA-BCN</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>STN-KIR</t>
+          <t>CDG-YVR</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>LTN-ORK</t>
+          <t>LBA-REU</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>LCA-ZRH</t>
+          <t>KEF-LHR</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>PEK-LHR</t>
+          <t>HEL-LHR</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>LTN-LCA</t>
+          <t>LCA-LGW</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>GLA-GVA</t>
+          <t>GLA-IBZ</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>CDG-YVR</t>
+          <t>LPL-CDG</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>BOS-DOH</t>
+          <t>PEK-LHR</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>LBA-REU</t>
+          <t>LTN-ORK</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>HEL-LHR</t>
+          <t>LHR-CAI</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>LCA-LGW</t>
+          <t>FCO-DFW</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>IST-IAD</t>
+          <t>LGW-LCA</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>LHR-CAI</t>
+          <t>BHX-RAK</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>RUH-IAD</t>
+          <t>BHX-LEI</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>FCO-DFW</t>
+          <t>MAN-BLQ</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>LBA-BCN</t>
+          <t>CVG-BAH</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>KRK-SNN</t>
+          <t>AGP-GLA</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>LHR-HND</t>
+          <t>MAN-DLM</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>REU-MAN</t>
+          <t>AUS-FRA</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>CVG-BAH</t>
+          <t>EWR-ATH</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>CGN-DUB</t>
+          <t>FCO-YYZ</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>DUB-DBV</t>
+          <t>LUX-ATL</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>DOH-BOS</t>
+          <t>LHR-CLT</t>
         </is>
       </c>
       <c r="C578" t="n">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>LHR-CLT</t>
+          <t>RUH-IAD</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>DUB-GVA</t>
+          <t>DUB-MAN</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>VIE-YYZ</t>
+          <t>DOH-BOS</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>FCO-YYZ</t>
+          <t>VIE-JFK</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>LUX-ATL</t>
+          <t>REU-MAN</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>GLA-IBZ</t>
+          <t>DUB-BLQ</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>DUB-MAN</t>
+          <t>DUB-GVA</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>AUS-FRA</t>
+          <t>BRS-WMI</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>MAN-BLQ</t>
+          <t>LGW-INV</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>BHX-LEI</t>
+          <t>DUB-DBV</t>
         </is>
       </c>
       <c r="C588" t="n">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>DUB-BLQ</t>
+          <t>CGN-DUB</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>VIE-JFK</t>
+          <t>LHR-HND</t>
         </is>
       </c>
       <c r="C590" t="n">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>BHX-RAK</t>
+          <t>KRK-SNN</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>BRS-WMI</t>
+          <t>IST-IAD</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>EWR-ATH</t>
+          <t>DTW-CDG</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>LGW-INV</t>
+          <t>YYZ-DOH</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>LGW-LCA</t>
+          <t>VIE-YYZ</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>BOD-LGW</t>
+          <t>LHR-AUH</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>CAI-LHR</t>
+          <t>TLV-YYZ</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>TLV-YYZ</t>
+          <t>CAI-LHR</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>BEG-JFK</t>
+          <t>BOD-LGW</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>ORK-POZ</t>
+          <t>BEG-JFK</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>CDG-SEA</t>
+          <t>ATH-PHL</t>
         </is>
       </c>
       <c r="C602" t="n">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>BUD-LHR</t>
+          <t>CDG-SEA</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>ATH-PHL</t>
+          <t>MAN-BZR</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>ATH-LGW</t>
+          <t>FAO-BHX</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EWR-DXB</t>
+          <t>MXP-DUB</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>STN-DUB</t>
+          <t>ALC-PIK</t>
         </is>
       </c>
       <c r="C607" t="n">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>LHR-IAH</t>
+          <t>ORK-POZ</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>VCE-LHR</t>
+          <t>YVR-LHR</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>YVR-LHR</t>
+          <t>VCE-LHR</t>
         </is>
       </c>
       <c r="C610" t="n">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>MAN-BZR</t>
+          <t>LHR-IAH</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>MXP-DUB</t>
+          <t>STN-DUB</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>FAO-BHX</t>
+          <t>EWR-DXB</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>ALC-PIK</t>
+          <t>MAN-OPO</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>LHR-AUH</t>
+          <t>ATH-LGW</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>MAN-OPO</t>
+          <t>BUD-LHR</t>
         </is>
       </c>
       <c r="C616" t="n">
